--- a/ValueSet-mesh-terms.xlsx
+++ b/ValueSet-mesh-terms.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T23:53:55+00:00</t>
+    <t>2025-12-03T18:37:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mesh-terms.xlsx
+++ b/ValueSet-mesh-terms.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T18:37:31+00:00</t>
+    <t>2025-12-03T22:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NCPI FHIR Working Group (http://example.org/example-publisher, ncpi-fhir-ig@googlegroups.com)</t>
+    <t>NCPI FHIR Working Group (https://www.ncpi-acc.org/about/working-groups, ncpi-fhir-ig@googlegroups.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-mesh-terms.xlsx
+++ b/ValueSet-mesh-terms.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T22:26:51+00:00</t>
+    <t>2026-01-13T18:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mesh-terms.xlsx
+++ b/ValueSet-mesh-terms.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T18:03:13+00:00</t>
+    <t>2026-02-06T18:07:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mesh-terms.xlsx
+++ b/ValueSet-mesh-terms.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T18:07:39+00:00</t>
+    <t>2026-03-09T20:11:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
